--- a/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_GRUPO CAESA SEGUROS FC CARTAGENA CB.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_GRUPO CAESA SEGUROS FC CARTAGENA CB.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V. FAVERANI TATSCH</t>
+          <t>A. GARUBA ALARI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>12.7115</v>
+        <v>2.9102</v>
       </c>
       <c r="E2" t="n">
-        <v>4.331600000000001</v>
+        <v>-0.4776000000000002</v>
       </c>
       <c r="F2" t="n">
-        <v>8.379799999999999</v>
+        <v>3.3874</v>
       </c>
       <c r="G2" t="n">
-        <v>-8.837399999999999</v>
+        <v>-7.904500000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>12.8749</v>
+        <v>14.7294</v>
       </c>
       <c r="I2" t="n">
-        <v>-21.7122</v>
+        <v>-22.634</v>
       </c>
       <c r="J2" t="n">
-        <v>27.0542</v>
+        <v>21.5737</v>
       </c>
       <c r="K2" t="n">
-        <v>26.9159</v>
+        <v>23.0232</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1384000000000007</v>
+        <v>-1.449999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-35.8917</v>
+        <v>-29.478</v>
       </c>
       <c r="N2" t="n">
-        <v>-14.0411</v>
+        <v>-8.293699999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>-21.8508</v>
+        <v>-21.184</v>
       </c>
       <c r="P2" t="n">
-        <v>-19.1408</v>
+        <v>4.5675</v>
       </c>
       <c r="Q2" t="n">
-        <v>-66.33929999999999</v>
+        <v>-39.3684</v>
       </c>
       <c r="R2" t="n">
-        <v>47.1988</v>
+        <v>43.9363</v>
       </c>
       <c r="S2" t="n">
-        <v>24.1283</v>
+        <v>1.1512</v>
       </c>
       <c r="T2" t="n">
-        <v>6.7277</v>
+        <v>-2.0365</v>
       </c>
       <c r="U2" t="n">
-        <v>17.4009</v>
+        <v>3.1878</v>
       </c>
       <c r="V2" t="n">
-        <v>16.5615</v>
+        <v>5.0954</v>
       </c>
       <c r="W2" t="n">
-        <v>36.8897</v>
+        <v>19.3544</v>
       </c>
       <c r="X2" t="n">
-        <v>-20.3283</v>
+        <v>-14.2589</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. GARUBA ALARI</t>
+          <t>K. WEBSTER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8282</v>
+        <v>-2.688199999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1074</v>
+        <v>7.5105</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7212999999999995</v>
+        <v>-10.1986</v>
       </c>
       <c r="G3" t="n">
-        <v>-7.904500000000001</v>
+        <v>1.921800000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>14.7294</v>
+        <v>1.596100000000002</v>
       </c>
       <c r="I3" t="n">
-        <v>-22.634</v>
+        <v>0.3262</v>
       </c>
       <c r="J3" t="n">
-        <v>21.5737</v>
+        <v>45.1898</v>
       </c>
       <c r="K3" t="n">
-        <v>23.0232</v>
+        <v>20.7087</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.449999999999999</v>
+        <v>24.4813</v>
       </c>
       <c r="M3" t="n">
-        <v>-29.478</v>
+        <v>-43.2677</v>
       </c>
       <c r="N3" t="n">
-        <v>-8.293699999999999</v>
+        <v>-19.1127</v>
       </c>
       <c r="O3" t="n">
-        <v>-21.184</v>
+        <v>-24.1551</v>
       </c>
       <c r="P3" t="n">
-        <v>4.5675</v>
+        <v>7.395199999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>-39.3684</v>
+        <v>-41.761</v>
       </c>
       <c r="R3" t="n">
-        <v>43.9363</v>
+        <v>49.1568</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0696</v>
+        <v>-8.217600000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5481999999999996</v>
+        <v>-9.7971</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5215000000000003</v>
+        <v>1.5796</v>
       </c>
       <c r="V3" t="n">
-        <v>5.0954</v>
+        <v>-3.7881</v>
       </c>
       <c r="W3" t="n">
-        <v>19.3544</v>
+        <v>13.8791</v>
       </c>
       <c r="X3" t="n">
-        <v>-14.2589</v>
+        <v>-17.6669</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>-5.587</v>
+        <v>-3.8457</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.652299999999999</v>
+        <v>-4.4469</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9346999999999999</v>
+        <v>0.6013999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1372999999999998</v>
@@ -766,13 +766,13 @@
         <v>14.1378</v>
       </c>
       <c r="S4" t="n">
-        <v>-5.5418</v>
+        <v>-3.8003</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.0058</v>
+        <v>-1.7999</v>
       </c>
       <c r="U4" t="n">
-        <v>-3.5364</v>
+        <v>-2</v>
       </c>
       <c r="V4" t="n">
         <v>-3.605799999999999</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. THOMAS</t>
+          <t>V. FAVERANI TATSCH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="D5" t="n">
-        <v>-12.246</v>
+        <v>-6.906599999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-7.7083</v>
+        <v>-6.3434</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.537700000000001</v>
+        <v>-0.5636000000000007</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4397</v>
+        <v>-8.837399999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3284</v>
+        <v>12.8749</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.8886</v>
+        <v>-21.7122</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6129</v>
+        <v>27.0542</v>
       </c>
       <c r="K5" t="n">
-        <v>6.1365</v>
+        <v>26.9159</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.5236</v>
+        <v>0.1384000000000007</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.1732</v>
+        <v>-35.8917</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8081</v>
+        <v>-14.0411</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.365200000000001</v>
+        <v>-21.8508</v>
       </c>
       <c r="P5" t="n">
-        <v>-8.2652</v>
+        <v>-19.1408</v>
       </c>
       <c r="Q5" t="n">
-        <v>-14.1379</v>
+        <v>-66.33929999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>5.8725</v>
+        <v>47.1988</v>
       </c>
       <c r="S5" t="n">
-        <v>-4.636200000000001</v>
+        <v>4.510199999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.3542</v>
+        <v>-3.9474</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.2821</v>
+        <v>8.4572</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2159</v>
+        <v>16.5615</v>
       </c>
       <c r="W5" t="n">
-        <v>4.1709</v>
+        <v>36.8897</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.9549</v>
+        <v>-20.3283</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. DOMENECH FONTANA</t>
+          <t>S. THOMAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>-15.2317</v>
+        <v>-10.5547</v>
       </c>
       <c r="E6" t="n">
-        <v>-16.3523</v>
+        <v>-6.9007</v>
       </c>
       <c r="F6" t="n">
-        <v>1.120299999999999</v>
+        <v>-3.653999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-28.8636</v>
+        <v>0.4397</v>
       </c>
       <c r="H6" t="n">
-        <v>-7.6245</v>
+        <v>4.3284</v>
       </c>
       <c r="I6" t="n">
-        <v>-21.2397</v>
+        <v>-3.8886</v>
       </c>
       <c r="J6" t="n">
-        <v>2.787399999999999</v>
+        <v>4.6129</v>
       </c>
       <c r="K6" t="n">
-        <v>9.737</v>
+        <v>6.1365</v>
       </c>
       <c r="L6" t="n">
-        <v>-6.949699999999998</v>
+        <v>-1.5236</v>
       </c>
       <c r="M6" t="n">
-        <v>-31.6512</v>
+        <v>-4.1732</v>
       </c>
       <c r="N6" t="n">
-        <v>-17.3611</v>
+        <v>-1.8081</v>
       </c>
       <c r="O6" t="n">
-        <v>-14.2899</v>
+        <v>-2.365200000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>17.1832</v>
+        <v>-8.2652</v>
       </c>
       <c r="Q6" t="n">
-        <v>-27.1881</v>
+        <v>-14.1379</v>
       </c>
       <c r="R6" t="n">
-        <v>44.3712</v>
+        <v>5.8725</v>
       </c>
       <c r="S6" t="n">
-        <v>-4.6515</v>
+        <v>-2.9451</v>
       </c>
       <c r="T6" t="n">
-        <v>-7.072900000000001</v>
+        <v>-1.5466</v>
       </c>
       <c r="U6" t="n">
-        <v>2.421</v>
+        <v>-1.3986</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1003</v>
+        <v>0.2159</v>
       </c>
       <c r="W6" t="n">
-        <v>15.1215</v>
+        <v>4.1709</v>
       </c>
       <c r="X6" t="n">
-        <v>-14.0209</v>
+        <v>-3.9549</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. KELLY</t>
+          <t>I. RIVERA CARROLL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>-16.8989</v>
+        <v>-13.6695</v>
       </c>
       <c r="E7" t="n">
-        <v>-9.2751</v>
+        <v>1.62</v>
       </c>
       <c r="F7" t="n">
-        <v>-7.6235</v>
+        <v>-15.2896</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.0988</v>
+        <v>-2.652200000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0769</v>
+        <v>1.3717</v>
       </c>
       <c r="I7" t="n">
-        <v>-6.1756</v>
+        <v>-4.024299999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>6.729699999999999</v>
+        <v>33.0981</v>
       </c>
       <c r="K7" t="n">
-        <v>4.807399999999999</v>
+        <v>19.4145</v>
       </c>
       <c r="L7" t="n">
-        <v>1.922000000000001</v>
+        <v>13.6833</v>
       </c>
       <c r="M7" t="n">
-        <v>-10.8282</v>
+        <v>-35.7503</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.7306</v>
+        <v>-18.043</v>
       </c>
       <c r="O7" t="n">
-        <v>-8.098000000000001</v>
+        <v>-17.7076</v>
       </c>
       <c r="P7" t="n">
-        <v>-6.960199999999999</v>
+        <v>4.5678</v>
       </c>
       <c r="Q7" t="n">
-        <v>-16.5304</v>
+        <v>-36.5408</v>
       </c>
       <c r="R7" t="n">
-        <v>9.5702</v>
+        <v>41.1087</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1654</v>
+        <v>-12.2076</v>
       </c>
       <c r="T7" t="n">
-        <v>-4.0149</v>
+        <v>-9.0113</v>
       </c>
       <c r="U7" t="n">
-        <v>2.8493</v>
+        <v>-3.1962</v>
       </c>
       <c r="V7" t="n">
-        <v>-4.674300000000001</v>
+        <v>-3.3774</v>
       </c>
       <c r="W7" t="n">
-        <v>4.5406</v>
+        <v>14.0741</v>
       </c>
       <c r="X7" t="n">
-        <v>-9.2148</v>
+        <v>-17.4516</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. WEBSTER</t>
+          <t>J. LOPEZ SANTANA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>-17.2069</v>
+        <v>-13.8696</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0611</v>
+        <v>-10.9813</v>
       </c>
       <c r="F8" t="n">
-        <v>-15.146</v>
+        <v>-2.888500000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>1.921800000000001</v>
+        <v>-1.9233</v>
       </c>
       <c r="H8" t="n">
-        <v>1.596100000000002</v>
+        <v>-3.7219</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3262</v>
+        <v>1.7985</v>
       </c>
       <c r="J8" t="n">
-        <v>45.1898</v>
+        <v>19.3649</v>
       </c>
       <c r="K8" t="n">
-        <v>20.7087</v>
+        <v>7.9574</v>
       </c>
       <c r="L8" t="n">
-        <v>24.4813</v>
+        <v>11.4075</v>
       </c>
       <c r="M8" t="n">
-        <v>-43.2677</v>
+        <v>-21.2881</v>
       </c>
       <c r="N8" t="n">
-        <v>-19.1127</v>
+        <v>-11.6793</v>
       </c>
       <c r="O8" t="n">
-        <v>-24.1551</v>
+        <v>-9.6089</v>
       </c>
       <c r="P8" t="n">
-        <v>7.395199999999999</v>
+        <v>-9.570399999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-41.761</v>
+        <v>-33.7136</v>
       </c>
       <c r="R8" t="n">
-        <v>49.1568</v>
+        <v>24.1432</v>
       </c>
       <c r="S8" t="n">
-        <v>-22.7364</v>
+        <v>-6.4955</v>
       </c>
       <c r="T8" t="n">
-        <v>-19.3685</v>
+        <v>-5.3231</v>
       </c>
       <c r="U8" t="n">
-        <v>-3.368</v>
+        <v>-1.1722</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.7881</v>
+        <v>4.119199999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>13.8791</v>
+        <v>8.6907</v>
       </c>
       <c r="X8" t="n">
-        <v>-17.6669</v>
+        <v>-4.5713</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. SUOKAS</t>
+          <t>A. DOMENECH FONTANA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D9" t="n">
-        <v>-20.4233</v>
+        <v>-15.777</v>
       </c>
       <c r="E9" t="n">
-        <v>-10.27</v>
+        <v>-16.3992</v>
       </c>
       <c r="F9" t="n">
-        <v>-10.1533</v>
+        <v>0.6222000000000003</v>
       </c>
       <c r="G9" t="n">
-        <v>-9.746</v>
+        <v>-28.8636</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.8628</v>
+        <v>-7.6245</v>
       </c>
       <c r="I9" t="n">
-        <v>-5.8833</v>
+        <v>-21.2397</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.8002</v>
+        <v>2.787399999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2576</v>
+        <v>9.737</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5425999999999996</v>
+        <v>-6.949699999999998</v>
       </c>
       <c r="M9" t="n">
-        <v>-7.945600000000001</v>
+        <v>-31.6512</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.605</v>
+        <v>-17.3611</v>
       </c>
       <c r="O9" t="n">
-        <v>-5.3407</v>
+        <v>-14.2899</v>
       </c>
       <c r="P9" t="n">
-        <v>-4.1325</v>
+        <v>17.1832</v>
       </c>
       <c r="Q9" t="n">
-        <v>-12.3979</v>
+        <v>-27.1881</v>
       </c>
       <c r="R9" t="n">
-        <v>8.2651</v>
+        <v>44.3712</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.6992</v>
+        <v>-5.1969</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.7426</v>
+        <v>-7.1198</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.9567</v>
+        <v>1.923</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.8455</v>
+        <v>1.1003</v>
       </c>
       <c r="W9" t="n">
-        <v>5.6705</v>
+        <v>15.1215</v>
       </c>
       <c r="X9" t="n">
-        <v>-8.5161</v>
+        <v>-14.0209</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. LOPEZ SANTANA</t>
+          <t>A. KELLY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>-21.0241</v>
+        <v>-16.5079</v>
       </c>
       <c r="E10" t="n">
-        <v>-15.9061</v>
+        <v>-7.0759</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.118</v>
+        <v>-9.431699999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9233</v>
+        <v>-4.0988</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.7219</v>
+        <v>2.0769</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7985</v>
+        <v>-6.1756</v>
       </c>
       <c r="J10" t="n">
-        <v>19.3649</v>
+        <v>6.729699999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>7.9574</v>
+        <v>4.807399999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>11.4075</v>
+        <v>1.922000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-21.2881</v>
+        <v>-10.8282</v>
       </c>
       <c r="N10" t="n">
-        <v>-11.6793</v>
+        <v>-2.7306</v>
       </c>
       <c r="O10" t="n">
-        <v>-9.6089</v>
+        <v>-8.098000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>-9.570399999999999</v>
+        <v>-6.960199999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>-33.7136</v>
+        <v>-16.5304</v>
       </c>
       <c r="R10" t="n">
-        <v>24.1432</v>
+        <v>9.5702</v>
       </c>
       <c r="S10" t="n">
-        <v>-13.6497</v>
+        <v>-0.7744</v>
       </c>
       <c r="T10" t="n">
-        <v>-10.2478</v>
+        <v>-1.8157</v>
       </c>
       <c r="U10" t="n">
-        <v>-3.4016</v>
+        <v>1.0412</v>
       </c>
       <c r="V10" t="n">
-        <v>4.119199999999999</v>
+        <v>-4.674300000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>8.6907</v>
+        <v>4.5406</v>
       </c>
       <c r="X10" t="n">
-        <v>-4.5713</v>
+        <v>-9.2148</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. RIVERA CARROLL</t>
+          <t>T. SUOKAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>-21.4008</v>
+        <v>-17.8974</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.748</v>
+        <v>-9.0334</v>
       </c>
       <c r="F11" t="n">
-        <v>-17.6528</v>
+        <v>-8.863799999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.652200000000001</v>
+        <v>-9.746</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3717</v>
+        <v>-3.8628</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.024299999999999</v>
+        <v>-5.8833</v>
       </c>
       <c r="J11" t="n">
-        <v>33.0981</v>
+        <v>-1.8002</v>
       </c>
       <c r="K11" t="n">
-        <v>19.4145</v>
+        <v>-1.2576</v>
       </c>
       <c r="L11" t="n">
-        <v>13.6833</v>
+        <v>-0.5425999999999996</v>
       </c>
       <c r="M11" t="n">
-        <v>-35.7503</v>
+        <v>-7.945600000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>-18.043</v>
+        <v>-2.605</v>
       </c>
       <c r="O11" t="n">
-        <v>-17.7076</v>
+        <v>-5.3407</v>
       </c>
       <c r="P11" t="n">
-        <v>4.5678</v>
+        <v>-4.1325</v>
       </c>
       <c r="Q11" t="n">
-        <v>-36.5408</v>
+        <v>-12.3979</v>
       </c>
       <c r="R11" t="n">
-        <v>41.1087</v>
+        <v>8.2651</v>
       </c>
       <c r="S11" t="n">
-        <v>-19.9388</v>
+        <v>-1.1731</v>
       </c>
       <c r="T11" t="n">
-        <v>-14.3793</v>
+        <v>-0.5059</v>
       </c>
       <c r="U11" t="n">
-        <v>-5.5596</v>
+        <v>-0.6672</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.3774</v>
+        <v>-2.8455</v>
       </c>
       <c r="W11" t="n">
-        <v>14.0741</v>
+        <v>5.6705</v>
       </c>
       <c r="X11" t="n">
-        <v>-17.4516</v>
+        <v>-8.5161</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. IDEHEN IDEHEN</t>
+          <t>A. MARTIN MARIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D12" t="n">
-        <v>-31.3081</v>
+        <v>-26.4227</v>
       </c>
       <c r="E12" t="n">
-        <v>-21.4743</v>
+        <v>-23.7178</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.833500000000001</v>
+        <v>-2.7048</v>
       </c>
       <c r="G12" t="n">
-        <v>-20.9956</v>
+        <v>9.439399999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-12.5691</v>
+        <v>2.997400000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-8.426399999999999</v>
+        <v>6.4419</v>
       </c>
       <c r="J12" t="n">
-        <v>2.7626</v>
+        <v>27.2214</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.531600000000001</v>
+        <v>11.815</v>
       </c>
       <c r="L12" t="n">
-        <v>6.293900000000001</v>
+        <v>15.4063</v>
       </c>
       <c r="M12" t="n">
-        <v>-23.7577</v>
+        <v>-17.7822</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.0375</v>
+        <v>-8.8178</v>
       </c>
       <c r="O12" t="n">
-        <v>-14.7208</v>
+        <v>-8.964600000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-7.6127</v>
+        <v>-16.3131</v>
       </c>
       <c r="Q12" t="n">
-        <v>-33.7132</v>
+        <v>-56.3343</v>
       </c>
       <c r="R12" t="n">
-        <v>26.1005</v>
+        <v>40.0209</v>
       </c>
       <c r="S12" t="n">
-        <v>14.3709</v>
+        <v>-12.4855</v>
       </c>
       <c r="T12" t="n">
-        <v>11.0267</v>
+        <v>-9.418700000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>3.3438</v>
+        <v>-3.067</v>
       </c>
       <c r="V12" t="n">
-        <v>-17.0705</v>
+        <v>-7.063099999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>-1.5502</v>
+        <v>14.8138</v>
       </c>
       <c r="X12" t="n">
-        <v>-15.5206</v>
+        <v>-21.8768</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>-32.5711</v>
+        <v>-29.9335</v>
       </c>
       <c r="E13" t="n">
-        <v>-24.5742</v>
+        <v>-22.7176</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.996799999999999</v>
+        <v>-7.2159</v>
       </c>
       <c r="G13" t="n">
         <v>-13.7596</v>
@@ -1468,13 +1468,13 @@
         <v>9.570300000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.754499999999999</v>
+        <v>-3.117</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.4247</v>
+        <v>-2.568</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.3297</v>
+        <v>-0.5489999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-8.9244</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. POLYNICE</t>
+          <t>A. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>-34.3001</v>
+        <v>-36.9555</v>
       </c>
       <c r="E14" t="n">
-        <v>-27.5861</v>
+        <v>-16.31</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.7136</v>
+        <v>-20.6454</v>
       </c>
       <c r="G14" t="n">
-        <v>-33.1822</v>
+        <v>-28.5444</v>
       </c>
       <c r="H14" t="n">
-        <v>-14.5389</v>
+        <v>-12.7086</v>
       </c>
       <c r="I14" t="n">
-        <v>-18.6436</v>
+        <v>-15.836</v>
       </c>
       <c r="J14" t="n">
-        <v>-11.8628</v>
+        <v>1.514</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.904000000000001</v>
+        <v>0.5975999999999992</v>
       </c>
       <c r="L14" t="n">
-        <v>-5.9596</v>
+        <v>0.9155000000000004</v>
       </c>
       <c r="M14" t="n">
-        <v>-21.3192</v>
+        <v>-30.0585</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.635300000000001</v>
+        <v>-13.3067</v>
       </c>
       <c r="O14" t="n">
-        <v>-12.684</v>
+        <v>-16.7517</v>
       </c>
       <c r="P14" t="n">
-        <v>8.4831</v>
+        <v>7.829899999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-20.0105</v>
+        <v>-17.1829</v>
       </c>
       <c r="R14" t="n">
-        <v>28.4934</v>
+        <v>25.0129</v>
       </c>
       <c r="S14" t="n">
-        <v>2.940300000000001</v>
+        <v>-3.2675</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2087</v>
+        <v>-2.4189</v>
       </c>
       <c r="U14" t="n">
-        <v>4.1493</v>
+        <v>-0.8483999999999998</v>
       </c>
       <c r="V14" t="n">
-        <v>-12.5409</v>
+        <v>-12.9741</v>
       </c>
       <c r="W14" t="n">
-        <v>5.496099999999999</v>
+        <v>1.7778</v>
       </c>
       <c r="X14" t="n">
-        <v>-18.0369</v>
+        <v>-14.7517</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. MARTIN MARIN</t>
+          <t>C. POLYNICE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>-37.136</v>
+        <v>-39.9864</v>
       </c>
       <c r="E15" t="n">
-        <v>-28.8982</v>
+        <v>-29.98</v>
       </c>
       <c r="F15" t="n">
-        <v>-8.2377</v>
+        <v>-10.0066</v>
       </c>
       <c r="G15" t="n">
-        <v>9.439399999999999</v>
+        <v>-33.1822</v>
       </c>
       <c r="H15" t="n">
-        <v>2.997400000000001</v>
+        <v>-14.5389</v>
       </c>
       <c r="I15" t="n">
-        <v>6.4419</v>
+        <v>-18.6436</v>
       </c>
       <c r="J15" t="n">
-        <v>27.2214</v>
+        <v>-11.8628</v>
       </c>
       <c r="K15" t="n">
-        <v>11.815</v>
+        <v>-5.904000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>15.4063</v>
+        <v>-5.9596</v>
       </c>
       <c r="M15" t="n">
-        <v>-17.7822</v>
+        <v>-21.3192</v>
       </c>
       <c r="N15" t="n">
-        <v>-8.8178</v>
+        <v>-8.635300000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-8.964600000000001</v>
+        <v>-12.684</v>
       </c>
       <c r="P15" t="n">
-        <v>-16.3131</v>
+        <v>8.4831</v>
       </c>
       <c r="Q15" t="n">
-        <v>-56.3343</v>
+        <v>-20.0105</v>
       </c>
       <c r="R15" t="n">
-        <v>40.0209</v>
+        <v>28.4934</v>
       </c>
       <c r="S15" t="n">
-        <v>-23.1994</v>
+        <v>-2.7462</v>
       </c>
       <c r="T15" t="n">
-        <v>-14.5992</v>
+        <v>-3.6026</v>
       </c>
       <c r="U15" t="n">
-        <v>-8.600099999999999</v>
+        <v>0.8567</v>
       </c>
       <c r="V15" t="n">
-        <v>-7.063099999999999</v>
+        <v>-12.5409</v>
       </c>
       <c r="W15" t="n">
-        <v>14.8138</v>
+        <v>5.496099999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>-21.8768</v>
+        <v>-18.0369</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. HARGUINDEY MANEIRO</t>
+          <t>E. IDEHEN IDEHEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-39.3772</v>
+        <v>-43.2621</v>
       </c>
       <c r="E16" t="n">
-        <v>-17.8891</v>
+        <v>-30.4437</v>
       </c>
       <c r="F16" t="n">
-        <v>-21.488</v>
+        <v>-12.8185</v>
       </c>
       <c r="G16" t="n">
-        <v>-28.5444</v>
+        <v>-20.9956</v>
       </c>
       <c r="H16" t="n">
-        <v>-12.7086</v>
+        <v>-12.5691</v>
       </c>
       <c r="I16" t="n">
-        <v>-15.836</v>
+        <v>-8.426399999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>1.514</v>
+        <v>2.7626</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5975999999999992</v>
+        <v>-3.531600000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9155000000000004</v>
+        <v>6.293900000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-30.0585</v>
+        <v>-23.7577</v>
       </c>
       <c r="N16" t="n">
-        <v>-13.3067</v>
+        <v>-9.0375</v>
       </c>
       <c r="O16" t="n">
-        <v>-16.7517</v>
+        <v>-14.7208</v>
       </c>
       <c r="P16" t="n">
-        <v>7.829899999999999</v>
+        <v>-7.6127</v>
       </c>
       <c r="Q16" t="n">
-        <v>-17.1829</v>
+        <v>-33.7132</v>
       </c>
       <c r="R16" t="n">
-        <v>25.0129</v>
+        <v>26.1005</v>
       </c>
       <c r="S16" t="n">
-        <v>-5.689</v>
+        <v>2.4169</v>
       </c>
       <c r="T16" t="n">
-        <v>-3.998</v>
+        <v>2.0574</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.6913</v>
+        <v>0.3593999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>-12.9741</v>
+        <v>-17.0705</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7778</v>
+        <v>-1.5502</v>
       </c>
       <c r="X16" t="n">
-        <v>-14.7517</v>
+        <v>-15.5206</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>-61.7897</v>
+        <v>-49.6998</v>
       </c>
       <c r="E17" t="n">
-        <v>-33.2318</v>
+        <v>-28.365</v>
       </c>
       <c r="F17" t="n">
-        <v>-28.5581</v>
+        <v>-21.3347</v>
       </c>
       <c r="G17" t="n">
         <v>-42.1762</v>
@@ -1780,13 +1780,13 @@
         <v>48.5038</v>
       </c>
       <c r="S17" t="n">
-        <v>-23.4466</v>
+        <v>-11.3564</v>
       </c>
       <c r="T17" t="n">
-        <v>-15.0619</v>
+        <v>-10.195</v>
       </c>
       <c r="U17" t="n">
-        <v>-8.3851</v>
+        <v>-1.1615</v>
       </c>
       <c r="V17" t="n">
         <v>6.4428</v>
@@ -1813,19 +1813,19 @@
         <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>-350.9612</v>
+        <v>-325.0664</v>
       </c>
       <c r="E18" t="n">
-        <v>-217.1879</v>
+        <v>-204.062</v>
       </c>
       <c r="F18" t="n">
-        <v>-133.7723</v>
+        <v>-121.0047</v>
       </c>
       <c r="G18" t="n">
         <v>-191.0202</v>
       </c>
       <c r="H18" t="n">
-        <v>-48.60569999999999</v>
+        <v>-48.6057</v>
       </c>
       <c r="I18" t="n">
         <v>-142.4154</v>
@@ -1837,7 +1837,7 @@
         <v>112.3576</v>
       </c>
       <c r="L18" t="n">
-        <v>71.0202</v>
+        <v>71.02020000000002</v>
       </c>
       <c r="M18" t="n">
         <v>-374.4004</v>
@@ -1858,13 +1858,13 @@
         <v>465.4624</v>
       </c>
       <c r="S18" t="n">
-        <v>-91.5994</v>
+        <v>-65.70480000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-82.17590000000001</v>
+        <v>-69.0491</v>
       </c>
       <c r="U18" t="n">
-        <v>-9.424799999999996</v>
+        <v>3.344800000000002</v>
       </c>
       <c r="V18" t="n">
         <v>-43.329</v>
